--- a/scripts/productos-digitales/guia-chocolateria/build/calculadora-capex-chocolateria.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/calculadora-capex-chocolateria.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +148,9 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
@@ -718,7 +721,7 @@
     <row r="6" ht="68" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1. Hoja «Parámetros»: los metros del local, el precio por m2 de la obra, los tipos de IVA, la renta, el horizonte de comparación y los kilos de plástico que importas. Todo lo que calcula el libro sale de aquí.</t>
+          <t>1. Hoja «Parámetros»: los metros del local, el precio por m² de la obra, los tipos de IVA, la renta, el horizonte de comparación y los kilos de plástico que importas. Todo lo que calcula el libro sale de aquí.</t>
         </is>
       </c>
     </row>
@@ -887,7 +890,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Comprar bien empieza por saber qué necesitas, no cuánto cuesta. Los dos libros comparten los mismos 75 m2 y la misma columna de IVA.</t>
+          <t>Comprar bien empieza por saber qué necesitas, no cuánto cuesta. Los dos libros comparten los mismos 75 m² y la misma columna de IVA.</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1110,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Los mismos 75 m2 del libro 1. Si los cambias, cambia la obra: es la única partida del CAPEX que no se teclea.</t>
+          <t>Los mismos 75 m² del libro 1. Si los cambias, cambia la obra: es la única partida del CAPEX que no se teclea.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Coste de obra y adecuación por m2</t>
+          <t>Coste de obra y adecuación por m²</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -1122,7 +1125,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>€/m2</t>
+          <t>€/m²</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1132,7 +1135,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO DECLARADO: ninguna fuente del research publica un coste de obra por m2 de obrador de chocolate. Es más barata que la de una pastelería por un motivo estructural, no por suerte: un obrador de chocolate NO genera humos, así que no hay conducto a cubierta ni la conversación con la comunidad de propietarios que lo acompaña. Pide tres presupuestos y sustitúyelo.</t>
+          <t>SUPUESTO DECLARADO: ninguna fuente del research publica un coste de obra por m² de obrador de chocolate. Es más barata que la de una pastelería por un motivo estructural, no por suerte: un obrador de chocolate NO genera humos, así que no hay conducto a cubierta ni la conversación con la comunidad de propietarios que lo acompaña. Pide tres presupuestos y sustitúyelo.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1161,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Superficie x precio por m2.</t>
+          <t>Superficie x precio por m².</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1261,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Supuesto para una ciudad media. La renta observada en los ocho traspasos verificados va de 910 euros/mes (`CHS-37b`, 74 m2 en Madrid-Vallecas) a 2.200 euros/mes (`CHS-38c`, 180 m2 en Barcelona); aqui se toma la parte baja porque ninguna de esas dos ciudades es una ciudad media.</t>
+          <t>Supuesto para una ciudad media. La renta observada en los ocho traspasos verificados va de 910 euros/mes (`CHS-37b`, 74 m² en Madrid-Vallecas) a 2.200 euros/mes (`CHS-38c`, 180 m² en Barcelona); aquí se toma la parte baja porque ninguna de esas dos ciudades es una ciudad media.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1502,7 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Los valores marcados «supuesto» son los de la bombonería de ejemplo «La Almendra» (75 m2 en una ciudad media española, obrador propio y tienda a calle). NO son datos de sector: son un punto de partida coherente para que puedas ver el libro funcionando antes de meter los tuyos.</t>
+          <t>Los valores marcados «supuesto» son los de la bombonería de ejemplo «La Almendra» (75 m² en una ciudad media española, obrador propio y tienda a calle). NO son datos de sector: son un punto de partida coherente para que puedas ver el libro funcionando antes de meter los tuyos.</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1669,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Obra y adecuacion del local (75 m2 x 380 euros/m2)</t>
+          <t>Obra y adecuación del local (75 m² x 380 euros/m²)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1719,12 +1722,12 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>La calcula «Parámetros» con tus metros y tu precio por m2</t>
+          <t>La calcula «Parámetros» con tus metros y tu precio por m²</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado: ninguna fuente del research publica un coste de obra por m2 de obrador de chocolate. Es mas barata que la de una pasteleria por un motivo estructural: un obrador de chocolate NO genera humos, asi que no hay conducto a cubierta ni la conversacion con la comunidad de propietarios que lo acompana. Publicar esta cifra como dato verificado esta prohibido (§5.1, 28).</t>
+          <t>SUPUESTO declarado: ninguna fuente del research publica un coste de obra por m² de obrador de chocolate. Es mas barata que la de una pastelería por un motivo estructural: un obrador de chocolate NO genera humos, así que no hay conducto a cubierta ni la conversación con la comunidad de propietarios que lo acompaña. Publicar esta cifra como dato verificado esta prohibido (§5.1, 28).</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1797,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. El corazon del obrador y la decision 2 del bonus 2. Base de IVA NO declarada: la ficha trae el indicio «/Neto» en la linea de embalaje, que no es confirmable. La escalera completa va de esta a la Cento EX de 100 kg (`CHS-41g`), y la eleccion la decide los kg/semana que salga en la hoja de capacidad del libro 1.</t>
+          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. El corazón del obrador y la decisión 2 del bonus 2. Base de IVA NO declarada: la ficha trae el indicio «/Neto» en la línea de embalaje, que no es confirmable. La escalera completa va de esta a la Cento EX de 100 kg (`CHS-41g`), y la elección la decide los kg/semana que salga en la hoja de capacidad del libro 1.</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1867,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. La linea que nadie presupuesta: es el 12 % del precio de la maquina. La ficha la marca «Neto», que es un INDICIO de base sin IVA, no una declaracion: por eso va como «no declarada».</t>
+          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. La línea que nadie presupuesta: es el 12 % del precio de la máquina. La ficha la marca «Neto», que es un INDICIO de base sin IVA, no una declaración: por eso va como «no declarada».</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2022,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Temperador de bano maria digital, 22 L — Utilcentre bano maria digital 22 L</t>
+          <t>Temperador de baño maria digital, 22 L — Utilcentre baño maria digital 22 L</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2074,7 +2077,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. Segunda linea de templado: sin ella no se trabajan dos coberturas a la vez.</t>
+          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. Segunda línea de templado: sin ella no se trabajan dos coberturas a la vez.</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2217,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>OPCIONAL: viene con «¿la compras?» en No. La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. NO esta en la dotacion de La Almendra: es la maquina del ESCENARIO B, el arranque minimo, y aparece para que el lector vea la escalera. Cubeta adicional, 165,30 euros (`CHS-41h`).</t>
+          <t>OPCIONAL: viene con «¿la compras?» en No. La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. NO esta en la dotación de La Almendra: es la máquina del ESCENARIO B, el arranque mínimo, y aparece para que el lector vea la escalera. Cubeta adicional, 165,30 euros (`CHS-41h`).</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2302,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Vitrina refrigerada especifica para chocolate — Docriluc WB-6-6-R</t>
+          <t>Vitrina refrigerada específica para chocolate — Docriluc WB-6-6-R</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2354,7 +2357,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>600x730x1380 mm. RANGO DE TRABAJO DEL EQUIPO: +14 a +17 grados C, con base SIN IVA declarada literalmente por la ficha. NO son los +2/+4 grados C de una vitrina de pasteleria, que arruina el bombon por condensacion, sugar bloom y perdida de brillo. El OBJETIVO OPERATIVO es otra cosa y lo pone el kit: 16-18 grados C y menos del 55 % de humedad. El semaforo del libro 5 solo avisa por encima de 20 grados C, y queda PROHIBIDO uno que ponga en rojo los 16-18 del propio kit. Precio de oferta (antes 3.487,00 euros): esta FECHADO el 12-09-2026 y puede caducar.</t>
+          <t>600x730x1380 mm. RANGO DE TRABAJO DEL EQUIPO: +14 a +17 °C, con base SIN IVA declarada literalmente por la ficha. NO son los +2/+4 °C de una vitrina de pastelería, que arruina el bombón por condensación, sugar bloom y perdida de brillo. El OBJETIVO OPERATIVO es otra cosa y lo pone el kit: 16-18 °C y menos del 55 % de humedad. El semáforo del libro 5 solo avisa por encima de 20 °C, y queda PROHIBIDO uno que ponga en rojo los 16-18 del propio kit. Precio de oferta (antes 3.487,00 euros): esta FECHADO el 12-09-2026 y puede caducar.</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Camara climatizada de chocolate, unos 6 m2</t>
+          <t>Cámara climatizada de chocolate, unos 6 m²</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2424,7 +2427,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO declarado: ninguna fuente del research publica el precio de una camara de chocolate. Celda verde con valor por defecto. No es una nevera: trabaja a 15-18 grados C y 50-60 % de humedad, y ese control de HUMEDAD es lo que la encarece frente a una camara de pasteleria.</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO declarado: ninguna fuente del research publica el precio de una cámara de chocolate. Celda verde con valor por defecto. No es una nevera: trabaja a 15-18 °C y 50-60 % de humedad, y ese control de HUMEDAD es lo que la encarece frente a una cámara de pastelería.</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2497,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO. Es la del RELLENO, a 0-4 grados C, no la del bombon acabado. Confundirlas es el error de metodo que la SPEC persigue.</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO. Es la del RELLENO, a 0-4 °C, no la del bombón acabado. Confundirlas es el error de método que la SPEC persigue.</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2512,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Moldes de policarbonato para bomboneria (24 unidades) — Chocolate World varios (CF0246, CW12064, CW1000L07)</t>
+          <t>Moldes de policarbonato para bombonería (24 unidades) — Chocolate World varios (CF0246, CW12064, CW1000L07)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2564,7 +2567,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. SE PUBLICA COMO RANGO (D23a). El unico dato medido es 24,20-42,83 euros/ud (`CHS-45a`): 24 moldes valen entre 580,80 y 1.027,92 euros. El valor por defecto (804,36) es el punto medio del rango, y es SUPUESTO. Escribir una multiplicacion con un precio unitario elegido a ojo esta prohibido. Y los moldes de policarbonato NO pagan el impuesto al plastico: no estan sujetos por el art. 73.d) de la Ley 7/2022 (`CHN-62c`), porque no se entregan junto con la mercancia.</t>
+          <t>La ficha NO declara si el precio lleva IVA: se trata como base imponible y SE MARCA, que es lo honesto. SE PUBLICA COMO RANGO (D23a). El único dato medido es 24,20-42,83 euros/ud (`CHS-45a`): 24 moldes valen entre 580,80 y 1.027,92 euros. El valor por defecto (804,36) es el punto medio del rango, y es SUPUESTO. Escribir una multiplicación con un precio unitario elegido a ojo esta prohibido. Y los moldes de policarbonato NO pagan el impuesto al plastico: no están sujetos por el art. 73.d) de la Ley 7/2022 (`CHN-62c`), porque no se entregan junto con la mercancía.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2637,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO: la web del proveedor de packaging verificado devolvio HTTP 403 y no publica precio (`CHS-54`). En bomboneria la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacen. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2652,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Mobiliario de tienda, mostrador y estanteria</t>
+          <t>Mobiliario de tienda, mostrador y estantería</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2774,7 +2777,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO. La impresora de etiquetas deja de ser opcional en cuanto una sola referencia sale envasada con etiqueta (D47). Y Verifactu no es 2026, es 2027: 1-ene para sociedades y 1-jul para autonomos (`CHN-75`).</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO. La impresora de etiquetas deja de ser opcional en cuanto una sola referencia sale envasada con etiqueta (D47). Y Verifactu no es 2026, es 2027: 1-ene para sociedades y 1-jul para autónomos (`CHN-75`).</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2792,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Climatizacion del obrador con deshumidificacion</t>
+          <t>Climatización del obrador con deshumidificación</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2844,7 +2847,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO declarado, y es la partida que nadie presupuesta. El libro 1 NO calcula carga termica (D33): no hay un solo coeficiente con fuente ni de transmitancia, ni por m3, ni de aportes, ni de renovaciones. Lo que hace es (a) un semaforo de coherencia entre la temperatura objetivo, la exterior de agosto de TU ciudad y la potencia frigorifica que te OFREZCA EL INSTALADOR, y (b) una ficha de preguntas para el instalador. PROHIBIDO el climatizador evaporativo: anade humedad, que es justo lo contrario de lo que necesita un obrador de chocolate.</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO declarado, y es la partida que nadie presupuesta. El libro 1 NO calcula carga térmica (D33): no hay un solo coeficiente con fuente ni de transmitancia, ni por m³, ni de aportes, ni de renovaciones. Lo que hace es (a) un semáforo de coherencia entre la temperatura objetivo, la exterior de agosto de TU ciudad y la potencia frigorífica que te OFREZCA EL INSTALADOR, y (b) una ficha de preguntas para el instalador. PROHIBIDO el climatizador evaporativo: añade humedad, que es justo lo contrario de lo que necesita un obrador de chocolate.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2917,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>OPCIONAL: viene con «¿la compras?» en No. Base SIN IVA declarada literalmente por la ficha. Solo entra en el escenario de taza y churros, que es OTRO negocio (D1): la Ley 12/2012 los separa sola, porque su Anexo incluye el epigrafe 644.5 de bombones y caramelos y NO contiene ningun grupo de la agrupacion 67, donde esta la chocolateria de taza (`CHN-49c`).</t>
+          <t>OPCIONAL: viene con «¿la compras?» en No. Base SIN IVA declarada literalmente por la ficha. Solo entra en el escenario de taza y churros, que es OTRO negocio (D1): la Ley 12/2012 los separa sola, porque su Anexo incluye el epígrafe 644.5 de bombones y caramelos y NO contiene ningún grupo de la agrupación 67, donde esta la chocolatería de taza (`CHN-49c`).</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2990,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>La fianza NO es un gasto: es un deposito que se recupera. Va en el CAPEX porque hay que tenerla el dia de la firma, y por eso no se amortiza.</t>
+          <t>La fianza NO es un gasto: es un deposito que se recupera. Va en el CAPEX porque hay que tenerla el día de la firma, y por eso no se amortiza.</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Proyecto tecnico visado</t>
+          <t>Proyecto técnico visado</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -3057,7 +3060,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado. `CHN-50` (coste de proyecto tecnico) esta en EXCLUIDOS de la verificacion legal: no hay fuente, y publicar una cifra de proyecto tecnico como dato verificado esta prohibido (§5.1, 28).</t>
+          <t>SUPUESTO declarado. `CHN-50` (coste de proyecto técnico) esta en EXCLUIDOS de la verificación legal: no hay fuente, y publicar una cifra de proyecto técnico como dato verificado esta prohibido (§5.1, 28).</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3130,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Las tasas municipales no llevan IVA y su importe cambia en cada ayuntamiento: es el numero que hay que ir a buscar, no copiar. Y ojo: ningun ayuntamiento puede exigirte LICENCIA PREVIA de instalacion, funcionamiento o actividad hasta 750 m2 de superficie util de exposicion y venta, porque el epigrafe 644.5 esta en el Anexo de la Ley 12/2012 (`CHN-49`, `CHN-49b`). Decir que tramite pide Madrid o Barcelona esta PROHIBIDO: no se ha abierto ninguna ordenanza.</t>
+          <t>Las tasas municipales no llevan IVA y su importe cambia en cada ayuntamiento: es el número que hay que ir a buscar, no copiar. Y ojo: ningún ayuntamiento puede exigirte LICENCIA PREVIA de instalación, funcionamiento o actividad hasta 750 m² de superficie útil de exposición y venta, porque el epígrafe 644.5 esta en el Anexo de la Ley 12/2012 (`CHN-49`, `CHN-49b`). Decir que trámite pide Madrid o Barcelona esta PROHIBIDO: no se ha abierto ninguna ordenanza.</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3145,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Comunicacion o declaracion responsable al registro autonomico</t>
+          <t>Comunicación o declaración responsable al registro autonómico</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -3197,7 +3200,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>NO es una licencia y NO habilita para abrir: es el tramite de informacion del minorista, que esta EXCLUIDO del RGSEAA (`CHN-39`). El importe es supuesto y en varias comunidades es gratuito; en la Comunitat Valenciana lleva tasa y es condicion unica y suficiente para iniciar la actividad, y en Madrid se presenta simultaneamente al inicio y no habilita (`CHN-43`).</t>
+          <t>NO es una licencia y NO habilita para abrir: es el trámite de información del minorista, que esta EXCLUIDO del RGSEAA (`CHN-39`). El importe es supuesto y en varias comunidades es gratuito; en la Comunitat Valenciana lleva tasa y es condición única y suficiente para iniciar la actividad, y en Madrid se presenta simultaneamente al inicio y no habilita (`CHN-43`).</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3215,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Fondo de maniobra traido del libro 7 (EUR)</t>
+          <t>Fondo de maniobra traído del libro 7 (EUR)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3270,7 +3273,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>LLEGA YA CALCULADO DEL LIBRO 7 por celda verde con fila de cuadre (cruce 2 &lt;- 7). El libro 2 NO pide «meses de colchon»: los dos factores del fondo -los meses y los gastos fijos del ano de crucero- viven en el libro 7. Es caja, no inversion, y por eso el «Resumen» publica DOS lineas: «CAPEX sin el fondo de maniobra» (la que viaja al libro 7) y «Del cual, fondo de maniobra».</t>
+          <t>LLEGA YA CALCULADO DEL LIBRO 7 por celda verde con fila de cuadre (cruce 2 &lt;- 7). El libro 2 NO pide «meses de colchón»: los dos factores del fondo -los meses y los gastos fijos del año de crucero- viven en el libro 7. Es caja, no inversión, y por eso el «Resumen» publica DOS líneas: «CAPEX sin el fondo de maniobra» (la que viaja al libro 7) y «Del cual, fondo de maniobra».</t>
         </is>
       </c>
     </row>
@@ -3711,14 +3714,14 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>Suma de las lineas con precio verificado: atemperadora Selmi One (`CHS-41a`) + puesta en marcha + enrobadora R200 (`CHS-42a`) + placa dosificadora (`CHS-42i`) + moldes en RANGO (`CHS-45a`) + temperador de bano maria (`CHS-41j`) + mantenedor «desde» (`CHS-41i`). Se publica como RANGO porque dos de sus sumandos no son numeros cerrados.</t>
+          <t>Suma de las líneas con precio verificado: atemperadora Selmi One (`CHS-41a`) + puesta en marcha + enrobadora R200 (`CHS-42a`) + placa dosificadora (`CHS-42i`) + moldes en RANGO (`CHS-45a`) + temperador de baño maria (`CHS-41j`) + mantenedor «desde» (`CHS-41i`). Se publica como RANGO porque dos de sus sumandos no son números cerrados.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="62" customHeight="1">
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Escenario B: arranque minimo viable</t>
+          <t>Escenario B: arranque mínimo viable</t>
         </is>
       </c>
       <c r="I59" s="10" t="n">
@@ -3739,7 +3742,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>5.670,69 a 5.894,25 euros aplicando a `CHS-47b` (5.740,29) el rango de moldes de D23a. El mantenedor es un «desde», asi que el techo solo puede subir. El suelo de 5.500 euros que se publico primero estaba 170 euros por debajo de lo que produce el propio metodo.</t>
+          <t>5.670,69 a 5.894,25 euros aplicando a `CHS-47b` (5.740,29) el rango de moldes de D23a. El mantenedor es un «desde», así que el techo solo puede subir. El suelo de 5.500 euros que se publico primero estaba 170 euros por debajo de lo que produce el propio método.</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3760,13 @@
     <row r="61" ht="90" customHeight="1">
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>¿Dónde cae respecto al escenario profesional de entrada?</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="str">
-        <f>IF(I60="","",IF(I60&lt;I58,"Por debajo del rango publicado",IF(I60&gt;J58,"Por encima del rango publicado","Dentro del rango publicado")))</f>
-        <v>Por debajo del rango publicado</v>
+          <t>¿Se puede comparar con el escenario profesional de entrada?</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>No comparable: tu cifra va en base imponible y el rango publicado es base MIXTA</t>
+        </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
@@ -3956,7 +3960,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Es el eje del producto y el caso que calcula la hoja «CAPEX por Bloque» entera: 60-100 m2 y 1-2 empleados. Las otras dos son columnas de escenario, no productos aparte.</t>
+          <t>Es el eje del producto y el caso que calcula la hoja «CAPEX por Bloque» entera: 60-100 m² y 1-2 empleados. Las otras dos son columnas de escenario, no productos aparte.</t>
         </is>
       </c>
     </row>
@@ -3983,15 +3987,14 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>SIN CIFRAS DE MAQUINARIA A PROPOSITO (D2): no existe precio publico verificado del tren bean-to-bar, y lo que se entrega es la lista de la compra y las preguntas que hay que hacer. Inventar el precio seria justo el patron que la casa prohibe.
-Y la variante SUBE DE VALOR por dos motivos legales: (1) si importas grano ERES OPERADOR a efectos del EUDR, con diligencia debida completa, declaracion presentada previamente y registro cinco anos (`CHN-25`), no operador posterior; (2) el TOSTADO te puede meter en el CAPCA, y la nota (2) de su Anexo sube de grupo C a B cuando la actividad se desarrolla a menos de 500 m de un NUCLEO DE POBLACION (`CHN-47b`), es decir, en ciudad SIEMPRE. Ojo: «cacao» y «chocolate» tienen 0 ocurrencias en el CAPCA, asi que encajar el tostado de cacao en «cafe o similares» es INTERPRETACION, no mencion expresa (`CHN-47`).</t>
+          <t>SIN CIFRAS DE MAQUINARIA A PROPÓSITO: no existe precio público verificado del tren bean-to-bar, y lo que se entrega es la lista de la compra y las preguntas que hay que hacer. Inventar el precio sería justo el patrón que la casa prohíbe. · Y la variante SUBE DE VALOR por dos motivos legales: (1) si importas grano ERES OPERADOR a efectos del EUDR, con diligencia debida completa, declaración presentada previamente y registro cinco años (CHN-25), no operador posterior; (2) el TOSTADO te puede meter en el CAPCA, y la nota (2) de su Anexo sube de grupo C a B cuando la actividad se desarrolla a menos de 500 m de un NÚCLEO DE POBLACIÓN (CHN-47b), es decir, en ciudad SIEMPRE. Ojo: «cacao» y «chocolate» tienen 0 ocurrencias en el CAPCA, así que encajar el tostado de cacao en «café o similares» es INTERPRETACIÓN, no mención expresa (CHN-47).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chocolateria de taza y churros</t>
+          <t>Chocolatería de taza y churros</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4019,9 +4022,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>ES OTRO NEGOCIO, y la norma lo separa sola (D1): el Anexo de la Ley 12/2012 incluye el epigrafe 644.5 «Comercio al por menor de bombones y caramelos» y NO contiene ningun grupo de la agrupacion 67, donde esta la chocolateria de taza (grupo 676). O sea que la bomboneria se libra de la licencia previa hasta 750 m2 y la chocolateria de taza no (`CHN-49`, `CHN-49b`, `CHN-49c`).
-Lo que SI aporta: el chocolate convierte una racion de churros de 2,50 euros en 3,50-4 euros, un 40-60 % mas de ticket (`CHS-32`), y el margen bruto del churro es del 85-90 % (`CHS-31`) - aunque un maestro churrero citado lo rebaja a «un poco mas del 50 %», y los dos numeros se publican con su por que, no se elige el mas bonito.
-Lo que cuesta: freidora, extraccion de humos y la licencia que la bomboneria se ahorra. Los precios de churrera, freidora y extraccion NO estan verificados (`CHS-49`).</t>
+          <t>ES OTRO NEGOCIO, y la norma lo separa sola: el Anexo de la Ley 12/2012 incluye el epígrafe 644.5 «Comercio al por menor de bombones y caramelos» y NO contiene ningún grupo de la agrupación 67, donde está la chocolatería de taza (grupo 676). O sea que la bombonería se libra de la licencia previa hasta 750 m² y la chocolatería de taza no (CHN-49, CHN-49b, CHN-49c). · Lo que SÍ aporta: el chocolate convierte una ración de churros de 2,50 euros en 3,50-4 euros, un 40-60 % más de ticket (CHS-32), y el margen bruto del churro es del 85-90 % (CHS-31) - aunque un maestro churrero citado lo rebaja a «un poco más del 50 %», y los dos números se publican con su por qué, no se elige el más bonito. · Lo que cuesta: freidora, extracción de humos y la licencia que la bombonería se ahorra. Los precios de churrera, freidora y extracción NO están verificados (CHS-49).</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4222,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Balanza de precision para la formulacion</t>
+          <t>Balanza de precisión para la formulación</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -4247,7 +4248,7 @@
     <row r="25" ht="52" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Precio de la maquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catalogos existen y estan verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
+          <t>Precio de la máquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -4271,7 +4272,7 @@
     <row r="27" ht="52" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Potencia electrica y si necesita trifasica.</t>
+          <t>Potencia eléctrica y si necesita trifasica.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -4283,7 +4284,7 @@
     <row r="28" ht="52" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Ruido en dB a un metro: el tostador y el winnower son los dos equipos ruidosos de un obrador que por lo demas es silencioso.</t>
+          <t>Ruido en dB a un metro: el tostador y el winnower son los dos equipos ruidosos de un obrador que por lo demás es silencioso.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -4465,7 +4466,7 @@
     <row r="40" ht="44" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Extraccion de humos</t>
+          <t>Extracción de humos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4524,7 +4525,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Si hay freidora de gas, inspeccion periodica obligatoria de la instalacion receptora CADA CINCO ANOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilacion y el volumen minimo del local (`CHN-48`).</t>
+          <t>Si hay freidora de gas, inspección periódica obligatoria de la instalación receptora CADA CINCO AÑOS, que en instalaciones de hasta 70 kW incluye los aparatos y comprueba la ventilación y el volumen mínimo del local (`CHN-48`).</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4560,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>m2 mínimos</t>
+          <t>m² mínimos</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -4600,7 +4601,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>orden de magnitud publicado por el portal de franquicias, no dato auditado — El local mas pequeno de todo el research: 55 m2. Prueba que el formato chocolate-boutique cabe donde una pasteleria no. Barcelona, 2012.</t>
+          <t>orden de magnitud publicado por el portal de franquicias, no dato auditado — El local mas pequeño de todo el research: 55 m². Prueba que el formato chocolate-boutique cabe donde una pastelería no. Barcelona, 2012.</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4634,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>HUECO DECLARADO: no hay ficha con id en el JSON comun — HUECO DELIBERADO. La SPEC menciona esta franquicia en D11 como segunda ficha admitida, pero al censar el JSON comun el 12-09-2026 NO existe ninguna entrada `CHS-*` con sus cifras: la unica ficha que la roza es `CHS-31`, que solo publica el margen bruto del churro. La regla de la casa es que ninguna cifra con pretension de dato real entra sin id, asi que aqui va la fila con la marca y SIN numeros. Si alguien quiere publicarlos, primero hay que crear su ficha con URL y fecha.</t>
+          <t>HUECO DECLARADO: no hay ficha con id en el JSON común — HUECO DELIBERADO. La SPEC menciona esta franquicia en D11 como segunda ficha admitida, pero al censar el JSON común el 12-09-2026 NO existe ninguna entrada `CHS-*` con sus cifras: la única ficha que la roza es `CHS-31`, que solo publica el margen bruto del churro. La regla de la casa es que ninguna cifra con pretensión de dato real entra sin id, así que aquí va la fila con la marca y SIN números. Si alguien quiere publicarlos, primero hay que crear su ficha con URL y fecha.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4669,7 @@
     <row r="51" ht="56" customHeight="1">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Canon mas royalty mas compra obligada a central: una franquicia es cuatro o cinco veces la inversion del formato independiente de `CHS-03`. La columna existe para que el lector compare, no para recomendar. Y toda cifra va con su etiqueta: es lo que publica un portal de franquicias, no una cuenta auditada.</t>
+          <t>Canon mas royalty mas compra obligada a central: una franquicia es cuatro o cinco veces la inversión del formato independiente de `CHS-03`. La columna existe para que el lector compare, no para recomendar. Y toda cifra va con su etiqueta: es lo que publica un portal de franquicias, no una cuenta auditada.</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4748,7 @@
     <row r="59" ht="80" customHeight="1">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>LA VARIANTE DE TAZA Y CHURROS ES OTRO NEGOCIO, Y LA NORMA LO SEPARA SOLA. El Anexo de la Ley 12/2012 incluye el epígrafe 644.5 «Comercio al por menor de bombones y caramelos» y NO contiene ningún grupo de la agrupación 67, donde está la chocolatería de taza: la bombonería se libra de la licencia previa hasta 750 m2 y la de taza no. Lo que sí aporta la taza es ticket: el chocolate convierte una ración de churros de 2,50 € en 3,50-4 €. Lo que cuesta es freidora, extracción de humos y la licencia que la bombonería se ahorra.</t>
+          <t>LA VARIANTE DE TAZA Y CHURROS ES OTRO NEGOCIO, Y LA NORMA LO SEPARA SOLA. El Anexo de la Ley 12/2012 incluye el epígrafe 644.5 «Comercio al por menor de bombones y caramelos» y NO contiene ningún grupo de la agrupación 67, donde está la chocolatería de taza: la bombonería se libra de la licencia previa hasta 750 m² y la de taza no. Lo que sí aporta la taza es ticket: el chocolate convierte una ración de churros de 2,50 € en 3,50-4 €. Lo que cuesta es freidora, extracción de humos y la licencia que la bombonería se ahorra.</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4868,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Sembrado con el caso más informativo del censo: 26.000 € por 90 m2 de pastelería-bombonería CON OBRADOR EQUIPADO y 40 años de clientela, en El Prat de Llobregat. Es un precio PEDIDO en un anuncio, no un precio pagado.</t>
+          <t>Sembrado con el caso más informativo del censo: 26.000 € por 90 m² de pastelería-bombonería CON OBRADOR EQUIPADO y 40 años de clientela, en El Prat de Llobregat. Es un precio PEDIDO en un anuncio, no un precio pagado.</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4888,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Un traspaso casi nunca se abre tal cual. En chocolate hay una partida que casi seguro falta: la CLIMATIZACIÓN con deshumidificación del obrador. Una pastelería traspasada tiene hornos, no clima de 18-20 grados C. Míralo con la ficha de visita del libro 1 en la mano.</t>
+          <t>Un traspaso casi nunca se abre tal cual. En chocolate hay una partida que casi seguro falta: la CLIMATIZACIÓN con deshumidificación del obrador. Una pastelería traspasada tiene hornos, no clima de 18-20 °C. Míralo con la ficha de visita del libro 1 en la mano.</t>
         </is>
       </c>
     </row>
@@ -4997,45 +4998,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Coste del traspaso a lo largo del horizonte</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>IFERROR(C6+C7+C8*12*C13,"")</f>
         <v>110000.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Coste de la obra nueva a lo largo del horizonte</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>IFERROR(C10+C11*12*C13,"")</f>
         <v>155794.99</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Renta pagada sin facturar, traspaso</t>
         </is>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <f>IFERROR(C8*C9,"")</f>
         <v>1100.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Renta pagada sin facturar, obra nueva</t>
         </is>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <f>IFERROR(C11*C12,"")</f>
         <v>5200.0</v>
       </c>
@@ -5125,7 +5126,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>€ por m2</t>
+          <t>€ por m²</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -5152,7 +5153,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Pasteleria-bomboneria con obrador (40+ anos)</t>
+          <t>Pastelería-bombonería con obrador (40+ años)</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
@@ -5191,7 +5192,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Pasteleria-bomboneria historica (34 anos)</t>
+          <t>Pastelería-bombonería historica (34 años)</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
@@ -5227,7 +5228,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Pasteleria-bomboneria con obrador a la vista</t>
+          <t>Pastelería-bombonería con obrador a la vista</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
@@ -5266,7 +5267,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Pasteleria con obrador profesional</t>
+          <t>Pastelería con obrador profesional</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
@@ -5297,12 +5298,12 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Llica d'Amunt (Barcelona)</t>
+          <t>Lliçà d'Amunt (Barcelona)</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Obrador de pasteleria y panaderia</t>
+          <t>Obrador de pastelería y panadería</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
@@ -5406,7 +5407,7 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mataro (Barcelona)</t>
+          <t>Mataró (Barcelona)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -5498,7 +5499,7 @@
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Cinco traspasos de pasteleria-bomboneria leidos el 12-09-2026 en portales de anuncios (`CHS-38a` a `CHS-38e`), mas los tres de churreria-chocolateria de `TRASPASOS_VARIANTE_TAZA`, que son de OTRO formato. El rango publicado va de 26.000 a 210.000 euros (`CHS-39`) y la renta observada de 910 a 2.200 euros/mes. Traspasar puede salir mas barato que montar de cero, y esa es la comparacion a cinco anos que hace el libro 2. Pero son precios PEDIDOS, no pagados.</t>
+          <t>Cinco traspasos de pasteleria-bomboneria leídos el 12-09-2026 en portales de anuncios (`CHS-38a` a `CHS-38e`), mas los tres de churreria-chocolateria de `TRASPASOS_VARIANTE_TAZA`, que son de OTRO formato. El rango publicado va de 26.000 a 210.000 euros (`CHS-39`) y la renta observada de 910 a 2.200 euros/mes. Traspasar puede salir mas barato que montar de cero, y esa es la comparación a cinco años que hace el libro 2. Pero son precios PEDIDOS, no pagados.</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5507,7 @@
     <row r="42" ht="68" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Y lo que ninguno de los ocho trae: la cuenta de resultados. Un traspaso se valora por lo que gana el negocio, no por lo que pide el anuncio. Pide los modelos 303 y 390 de los tres últimos años y el resumen de la Seguridad Social de la plantilla; si no te los enseñan, ya sabes lo que estás comprando. Y en chocolate, una pregunta más: qué clima tiene el obrador hoy. Un obrador de pastelería traspasado no viene climatizado a 18-20 grados C, y esa partida no está en el precio del anuncio.</t>
+          <t>Y lo que ninguno de los ocho trae: la cuenta de resultados. Un traspaso se valora por lo que gana el negocio, no por lo que pide el anuncio. Pide los modelos 303 y 390 de los tres últimos años y el resumen de la Seguridad Social de la plantilla; si no te los enseñan, ya sabes lo que estás comprando. Y en chocolate, una pregunta más: qué clima tiene el obrador hoy. Un obrador de pastelería traspasado no viene climatizado a 18-20 °C, y esa partida no está en el precio del anuncio.</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5952,7 @@
           <t>Kg al mes de plástico no reciclado IMPORTADO o adquirido en otro país de la UE</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>'Parámetros'!B19</f>
         <v>3.2</v>
       </c>
@@ -5967,7 +5968,7 @@
           <t>Umbral de la exención del art. 75.f)</t>
         </is>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="23">
         <f>'Parámetros'!B20</f>
         <v>5.0</v>
       </c>
@@ -6171,7 +6172,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Metros por el precio por m2. Es la única partida del CAPEX que no se teclea, y la que más se desvía en la ejecución: lo que no está en el proyecto se paga aparte.</t>
+          <t>Metros por el precio por m². Es la única partida del CAPEX que no se teclea, y la que más se desvía en la ejecución: lo que no está en el proyecto se paga aparte.</t>
         </is>
       </c>
     </row>

--- a/scripts/productos-digitales/guia-chocolateria/build/calculadora-capex-chocolateria.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/calculadora-capex-chocolateria.xlsx
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Temperador de baño maria digital, 22 L — Utilcentre baño maria digital 22 L</t>
+          <t>Temperador de baño maría digital, 22 L — Utilcentre baño maría digital 22 L</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>SUPUESTO, no precio de ficha. SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de Espana, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
+          <t>SUPUESTO, no precio de ficha. SUPUESTO: la web del proveedor de packaging verificado devolvió HTTP 403 y no publica precio (`CHS-54`). En bombonería la caja ES el producto en campana, y el personalizado obliga a pedidos grandes: es dinero parado en el almacén. Si lo compras fuera de España, mira el contador de plastico del libro 2 (`PLASTICO`).</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TPV, ordenador, impresora de etiquetas y rotulo</t>
+          <t>TPV, ordenador, impresora de etiquetas y rótulo</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>Suma de las líneas con precio verificado: atemperadora Selmi One (`CHS-41a`) + puesta en marcha + enrobadora R200 (`CHS-42a`) + placa dosificadora (`CHS-42i`) + moldes en RANGO (`CHS-45a`) + temperador de baño maria (`CHS-41j`) + mantenedor «desde» (`CHS-41i`). Se publica como RANGO porque dos de sus sumandos no son números cerrados.</t>
+          <t>Suma de las líneas con precio verificado: atemperadora Selmi One (`CHS-41a`) + puesta en marcha + enrobadora R200 (`CHS-42a`) + placa dosificadora (`CHS-42i`) + moldes en RANGO (`CHS-45a`) + temperador de baño maría (`CHS-41j`) + mantenedor «desde» (`CHS-41i`). Se publica como RANGO porque dos de sus sumandos no son números cerrados.</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
     <row r="25" ht="52" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Precio de la máquina puesta en Espana, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
+          <t>Precio de la máquina puesta en España, con transporte, aduana y puesta en marcha desglosados: los catálogos existen y están verificados, pero los precios NO son publicos (venta a presupuesto o tienda fuera de la UE).</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -4260,7 +4260,7 @@
     <row r="26" ht="52" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Plazo de entrega real y quien hace el mantenimiento en Espana.</t>
+          <t>Plazo de entrega real y quien hace el mantenimiento en España.</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Pastelería-bombonería historica (34 años)</t>
+          <t>Pastelería-bombonería histórica (34 años)</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
